--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486385_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486385_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1019</v>
+        <v>5.1665</v>
       </c>
       <c r="E2" t="n">
-        <v>2.184</v>
+        <v>4.2001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9179</v>
+        <v>0.9663</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6648</v>
+        <v>2.3295</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2257</v>
+        <v>2.4634</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4391</v>
+        <v>-0.1338</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3206</v>
+        <v>1.6596</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2441</v>
+        <v>1.9225</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0765</v>
+        <v>-0.2629</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3442</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0184</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3626</v>
+        <v>0.1291</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0875</v>
+        <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2419</v>
+        <v>-1.5105</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7557</v>
+        <v>-0.3268</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4862</v>
+        <v>-1.1837</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1952</v>
+        <v>2.8249</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>3.9549</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0258</v>
+        <v>2.3293</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3061</v>
+        <v>0.8429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7198</v>
+        <v>1.4864</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3295</v>
+        <v>1.6648</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4634</v>
+        <v>1.2257</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1338</v>
+        <v>0.4391</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6596</v>
+        <v>1.3206</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9225</v>
+        <v>1.2441</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2629</v>
+        <v>0.0765</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.3442</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5407999999999999</v>
+        <v>-0.0184</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1291</v>
+        <v>0.3626</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6101</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.6512</v>
+        <v>0.4693</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2209</v>
+        <v>0.4146</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4303</v>
+        <v>0.0547</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8249</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>3.9549</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3342</v>
+        <v>1.0992</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5668</v>
+        <v>-0.6785</v>
       </c>
       <c r="F4" t="n">
-        <v>1.901</v>
+        <v>1.7777</v>
       </c>
       <c r="G4" t="n">
         <v>0.1287</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8804</v>
+        <v>0.6453</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5312</v>
+        <v>0.4194</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3492</v>
+        <v>0.2259</v>
       </c>
       <c r="V4" t="n">
         <v>0.7602</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6895</v>
+        <v>0.6393</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2173</v>
+        <v>-0.3291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9684</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1157</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5001</v>
+        <v>0.45</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2656</v>
+        <v>0.1538</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2346</v>
+        <v>0.2962</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1627</v>
+        <v>-0.3956</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4955</v>
+        <v>0.4609</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3328</v>
+        <v>-0.8565</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.182</v>
+        <v>-0.4578</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1015</v>
+        <v>-0.0793</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0805</v>
+        <v>-0.3785</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.0457</v>
+        <v>-0.1166</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.1987</v>
+        <v>-0.6721</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153</v>
+        <v>0.5554</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1364</v>
+        <v>-0.3412</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.5927</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2335</v>
+        <v>-0.9339</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4543</v>
+        <v>-1.0905</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6377</v>
+        <v>-0.1826</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1834</v>
+        <v>-0.9079</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>D. SANADZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4612</v>
+        <v>-1.2763</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1493</v>
+        <v>-2.6875</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6881</v>
+        <v>1.4113</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7956</v>
+        <v>-2.0303</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2227</v>
+        <v>-2.1714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4271</v>
+        <v>0.141</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5229</v>
+        <v>-1.8421</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5229</v>
+        <v>-1.1735</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.6686</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2727</v>
+        <v>-0.1882</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6998</v>
+        <v>-0.9978</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4271</v>
+        <v>0.8096</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>1.509</v>
+        <v>0.1015</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2882</v>
+        <v>0.0469</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2207</v>
+        <v>0.0547</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8927</v>
+        <v>-1.5595</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0979</v>
+        <v>-3.1551</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7949000000000001</v>
+        <v>1.5956</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4578</v>
+        <v>-0.7956</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0793</v>
+        <v>-1.2227</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3785</v>
+        <v>0.4271</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1166</v>
+        <v>-0.5229</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6721</v>
+        <v>-0.5229</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5554</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3412</v>
+        <v>-0.2727</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5927</v>
+        <v>-0.6998</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9339</v>
+        <v>0.4271</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5877</v>
+        <v>0.4107</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.2824</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8462</v>
+        <v>0.1283</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3698</v>
+        <v>-0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7602</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2885</v>
+        <v>-1.8916</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3677</v>
+        <v>-2.0324</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1408</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6276</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3134</v>
+        <v>0.0835</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2055</v>
+        <v>0.1298</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SANADZE</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.467</v>
+        <v>-2.1358</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6933</v>
+        <v>-2.2836</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2263</v>
+        <v>0.1478</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0303</v>
+        <v>-2.182</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1714</v>
+        <v>-2.1015</v>
       </c>
       <c r="I10" t="n">
-        <v>0.141</v>
+        <v>-0.0805</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8421</v>
+        <v>-2.0457</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1735</v>
+        <v>-2.1987</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6686</v>
+        <v>0.153</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1882</v>
+        <v>-0.1364</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9978</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8096</v>
+        <v>-0.2335</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0892</v>
+        <v>0.4813</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9589</v>
+        <v>0.8496</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1303</v>
+        <v>-0.3683</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5749</v>
+        <v>-2.4323</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2071</v>
+        <v>-2.0953</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3678</v>
+        <v>-0.337</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7445000000000001</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0479</v>
+        <v>0.0946</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U11" t="n">
-        <v>0.363</v>
+        <v>0.3939</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0235</v>
+        <v>-3.0485</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2798</v>
+        <v>-4.274</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2563</v>
+        <v>1.2255</v>
       </c>
       <c r="G12" t="n">
         <v>0.7259</v>
@@ -1390,13 +1390,13 @@
         <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8772</v>
+        <v>-0.9022</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2894</v>
+        <v>-0.2836</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5878</v>
+        <v>-0.6186</v>
       </c>
       <c r="V12" t="n">
         <v>0.3904</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7768</v>
+        <v>-6.9907</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1161</v>
+        <v>-5.6691</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6606</v>
+        <v>-1.3216</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0078</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.074</v>
+        <v>-1.2879</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8099</v>
+        <v>-0.3629</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2641</v>
+        <v>-0.925</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.4959</v>
+        <v>-10.496</v>
       </c>
       <c r="E14" t="n">
         <v>-17.7007</v>
       </c>
       <c r="F14" t="n">
-        <v>7.2049</v>
+        <v>7.204700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-8.112400000000001</v>
@@ -1528,16 +1528,16 @@
         <v>-0.4461999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3244000000000001</v>
+        <v>-0.3244000000000003</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.105500000000001</v>
+        <v>-3.1055</v>
       </c>
       <c r="O14" t="n">
         <v>2.781</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0001000000000001555</v>
+        <v>-9.999999999926734e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.4005</v>
@@ -1549,16 +1549,16 @@
         <v>-2.0549</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8414000000000009</v>
+        <v>0.8414000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.8963</v>
+        <v>-2.896100000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3285000000000005</v>
       </c>
       <c r="W14" t="n">
-        <v>6.646599999999999</v>
+        <v>6.646600000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-6.975099999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9922</v>
+        <v>7.0701</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2908</v>
+        <v>2.5144</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7013</v>
+        <v>4.5558</v>
       </c>
       <c r="G15" t="n">
         <v>7.4202</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8972</v>
+        <v>0.9752</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2151</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9056</v>
+        <v>0.7601</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3252</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.2425</v>
+        <v>4.509</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4311</v>
+        <v>1.6631</v>
       </c>
       <c r="F16" t="n">
-        <v>4.8114</v>
+        <v>2.8458</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.5637</v>
+        <v>2.5641</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.7613</v>
+        <v>1.7426</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1976</v>
+        <v>0.8216</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.2791</v>
+        <v>0.4478</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.8346</v>
+        <v>1.1164</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5554</v>
+        <v>-0.6686</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7154</v>
+        <v>2.1163</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0732</v>
+        <v>0.6262</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3578</v>
+        <v>1.4901</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2626</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>5.9792</v>
+        <v>-0.1427</v>
       </c>
       <c r="T16" t="n">
-        <v>5.6901</v>
+        <v>0.0853</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2891</v>
+        <v>-0.228</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8695</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5443</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7748</v>
+        <v>4.2684</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7749</v>
+        <v>1.4102</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.8582</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5641</v>
+        <v>3.398</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7426</v>
+        <v>2.0649</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8216</v>
+        <v>1.3331</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4478</v>
+        <v>1.5191</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1164</v>
+        <v>0.2952</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6686</v>
+        <v>1.224</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1163</v>
+        <v>1.8789</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6262</v>
+        <v>1.7697</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4901</v>
+        <v>0.1091</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1232</v>
+        <v>0.828</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1971</v>
+        <v>0.9361</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.1082</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
         <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3686</v>
+        <v>3.2322</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6337</v>
+        <v>0.4934</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7349</v>
+        <v>2.7388</v>
       </c>
       <c r="G18" t="n">
-        <v>3.398</v>
+        <v>6.4494</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0649</v>
+        <v>5.9036</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3331</v>
+        <v>0.5458</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5191</v>
+        <v>5.134</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2952</v>
+        <v>5.2288</v>
       </c>
       <c r="L18" t="n">
-        <v>1.224</v>
+        <v>-0.0948</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8789</v>
+        <v>1.3154</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7697</v>
+        <v>0.6748</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1091</v>
+        <v>0.6407</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0875</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-5.6552</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>2.8276</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9282</v>
+        <v>-0.1944</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1596</v>
+        <v>-0.1153</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2315</v>
+        <v>-0.079</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W18" t="n">
         <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5033</v>
+        <v>2.4685</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6241</v>
+        <v>-2.3687</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1274</v>
+        <v>4.8371</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4494</v>
+        <v>-3.5637</v>
       </c>
       <c r="H19" t="n">
-        <v>5.9036</v>
+        <v>-3.7613</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5458</v>
+        <v>0.1976</v>
       </c>
       <c r="J19" t="n">
-        <v>5.134</v>
+        <v>-4.2791</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2288</v>
+        <v>-4.8346</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0948</v>
+        <v>0.5554</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3154</v>
+        <v>0.7154</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6748</v>
+        <v>1.0732</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6407</v>
+        <v>-0.3578</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.8276</v>
+        <v>1.9576</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.6552</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8276</v>
+        <v>3.2626</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9233</v>
+        <v>2.2051</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2329</v>
+        <v>1.8903</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6904</v>
+        <v>0.3148</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1952</v>
+        <v>1.8695</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.549</v>
+        <v>0.0566</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0581</v>
+        <v>-1.9406</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5091</v>
+        <v>1.9972</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5728</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.216</v>
+        <v>0.3897</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.3761</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4746</v>
+        <v>0.0135</v>
       </c>
       <c r="V20" t="n">
         <v>0.3698</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0421</v>
+        <v>-1.5142</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4041</v>
+        <v>0.1547</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.638</v>
+        <v>-1.6689</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2303</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6166</v>
+        <v>-0.0886</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.536</v>
+        <v>0.0228</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0806</v>
+        <v>-0.1115</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4499</v>
+        <v>-3.7255</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7175</v>
+        <v>-4.2705</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2676</v>
+        <v>0.545</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6208</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1766</v>
+        <v>-0.4521</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5601</v>
+        <v>-0.2827</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3446</v>
+        <v>-5.1243</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5314</v>
+        <v>-4.8608</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8132</v>
+        <v>-0.2635</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7315</v>
@@ -2248,13 +2248,13 @@
         <v>2.6101</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9404</v>
+        <v>-0.7201</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0154</v>
+        <v>-0.3449</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.925</v>
+        <v>-0.3752</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8902</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.4958</v>
+        <v>11.2408</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.204699999999999</v>
+        <v>-7.204800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>17.7005</v>
+        <v>18.4455</v>
       </c>
       <c r="G24" t="n">
         <v>8.1126</v>
@@ -2299,22 +2299,22 @@
         <v>-2.3348</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3245</v>
+        <v>0.3245000000000005</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1055</v>
+        <v>3.105500000000001</v>
       </c>
       <c r="L24" t="n">
         <v>-2.7809</v>
       </c>
       <c r="M24" t="n">
-        <v>7.787899999999999</v>
+        <v>7.7879</v>
       </c>
       <c r="N24" t="n">
-        <v>7.3419</v>
+        <v>7.341900000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4460999999999998</v>
+        <v>0.4460999999999996</v>
       </c>
       <c r="P24" t="n">
         <v>1.942890293094024e-16</v>
@@ -2326,13 +2326,13 @@
         <v>17.4005</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0549</v>
+        <v>2.8001</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8962</v>
+        <v>2.8961</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8414000000000001</v>
+        <v>-0.09619999999999995</v>
       </c>
       <c r="V24" t="n">
         <v>0.3285</v>
@@ -2341,7 +2341,7 @@
         <v>6.975199999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.646699999999999</v>
+        <v>-6.6467</v>
       </c>
     </row>
   </sheetData>
